--- a/Auto Finan/LLM_Integration/field_type_mapping.xlsx
+++ b/Auto Finan/LLM_Integration/field_type_mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FH\source\repos\Auto Finan\Auto Finan\LLM_Integration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9E0A27-B64D-447C-B64C-FA0AA78992DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{533F4B44-D2CC-4701-B83A-720B06F24FC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="340" yWindow="4810" windowWidth="19200" windowHeight="5730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2710" windowWidth="19200" windowHeight="5730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="85">
   <si>
     <t>json字段</t>
   </si>
@@ -144,96 +144,181 @@
     <t>起始时间</t>
   </si>
   <si>
+    <t>飞机票</t>
+  </si>
+  <si>
+    <t>火车票</t>
+  </si>
+  <si>
+    <t>其他交通费</t>
+  </si>
+  <si>
+    <t>住宿费</t>
+  </si>
+  <si>
+    <t>是否安排伙食</t>
+  </si>
+  <si>
+    <t>是否安排交通</t>
+  </si>
+  <si>
+    <t>i</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>姓名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>travelPerson[].ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>travelPerson[].workUnit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>travelPerson[].title</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>travelPerson[].name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>travelPerson[].personType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人员类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>travelExpenses[].province</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>travelExpenses[].startTime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>travelExpenses[].endTime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>travelExpenses[].airfare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>travelExpenses[].trainfare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>travelExpenses[].otherTransport</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>travelExpenses[].accommodation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>travelExpenses[].mealArranged</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>travelExpenses[].transportArranged</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>laborInfo.laborType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>laborInfo.reason</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>laborInfo.personnelCategory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人员类别</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发放事由</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>劳务费类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>结束时间</t>
-  </si>
-  <si>
-    <t>飞机票</t>
-  </si>
-  <si>
-    <t>火车票</t>
-  </si>
-  <si>
-    <t>其他交通费</t>
-  </si>
-  <si>
-    <t>住宿费</t>
-  </si>
-  <si>
-    <t>是否安排伙食</t>
-  </si>
-  <si>
-    <t>是否安排交通</t>
-  </si>
-  <si>
-    <t>i</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>姓名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>travelPerson[].ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>travelPerson[].workUnit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>travelPerson[].title</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>travelPerson[].name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>travelPerson[].personType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>c</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>人员类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>travelExpenses[].province</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>travelExpenses[].startTime</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>travelExpenses[].endTime</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>travelExpenses[].airfare</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>travelExpenses[].trainfare</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>travelExpenses[].otherTransport</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>travelExpenses[].accommodation</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>travelExpenses[].mealArranged</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>travelExpenses[].transportArranged</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>laborInfo.remunerationNature</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>酬金性质</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>酬金信息备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>laborInfo.remarks</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发放标准</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>laborInfo.paymentStandard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>laborInfo.startTime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>laborInfo.endTime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开始时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>d</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>laborPerson.employeeId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>laborPerson.singleEntryAmount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工号/证件号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单笔录入金额</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -559,10 +644,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -730,7 +815,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s">
         <v>4</v>
@@ -741,7 +826,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
         <v>4</v>
@@ -752,7 +837,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -763,18 +848,18 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" t="s">
         <v>52</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>53</v>
-      </c>
-      <c r="C19" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -785,7 +870,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B21" t="s">
         <v>27</v>
@@ -796,90 +881,200 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B22" t="s">
         <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B23" t="s">
         <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B24" t="s">
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B25" t="s">
         <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B26" t="s">
         <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" t="s">
         <v>46</v>
       </c>
-      <c r="C29" t="s">
-        <v>47</v>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>64</v>
+      </c>
+      <c r="B31" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>65</v>
+      </c>
+      <c r="B32" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" t="s">
+        <v>52</v>
+      </c>
+      <c r="C33" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>73</v>
+      </c>
+      <c r="B34" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35" t="s">
+        <v>45</v>
+      </c>
+      <c r="C35" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>76</v>
+      </c>
+      <c r="B36" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>77</v>
+      </c>
+      <c r="B37" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>81</v>
+      </c>
+      <c r="B38" t="s">
+        <v>45</v>
+      </c>
+      <c r="C38" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>82</v>
+      </c>
+      <c r="B39" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/Auto Finan/LLM_Integration/field_type_mapping.xlsx
+++ b/Auto Finan/LLM_Integration/field_type_mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FH\source\repos\Auto Finan\Auto Finan\LLM_Integration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{533F4B44-D2CC-4701-B83A-720B06F24FC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{024AE66E-E27B-4F92-BDE4-9D53760DB6B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2710" windowWidth="19200" windowHeight="5730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="86">
   <si>
     <t>json字段</t>
   </si>
@@ -99,9 +99,6 @@
     <t>personnel[].bankCard</t>
   </si>
   <si>
-    <t>银行卡号</t>
-  </si>
-  <si>
     <t>personnel[].amount</t>
   </si>
   <si>
@@ -319,6 +316,14 @@
   </si>
   <si>
     <t>单笔录入金额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>银行卡号尾号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>empty</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -763,15 +768,15 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
         <v>4</v>
@@ -782,299 +787,299 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" t="s">
         <v>26</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>27</v>
-      </c>
-      <c r="C13" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
         <v>29</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>30</v>
-      </c>
-      <c r="C14" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" t="s">
         <v>32</v>
-      </c>
-      <c r="B15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s">
         <v>4</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
         <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" t="s">
         <v>51</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>52</v>
-      </c>
-      <c r="C19" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B23" t="s">
         <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B24" t="s">
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B25" t="s">
         <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B26" t="s">
         <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B29" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" t="s">
         <v>45</v>
-      </c>
-      <c r="C29" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>64</v>
+      </c>
+      <c r="B32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" t="s">
         <v>65</v>
-      </c>
-      <c r="B32" t="s">
-        <v>52</v>
-      </c>
-      <c r="C32" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>69</v>
+      </c>
+      <c r="B33" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33" t="s">
         <v>70</v>
-      </c>
-      <c r="B33" t="s">
-        <v>52</v>
-      </c>
-      <c r="C33" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C35" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B36" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C36" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C37" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C39" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/Auto Finan/LLM_Integration/field_type_mapping.xlsx
+++ b/Auto Finan/LLM_Integration/field_type_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FH\source\repos\Auto Finan\Auto Finan\LLM_Integration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{024AE66E-E27B-4F92-BDE4-9D53760DB6B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31E63340-D823-4A75-AE5D-304A2EC170C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="87">
   <si>
     <t>json字段</t>
   </si>
@@ -138,9 +138,6 @@
     <t>省份</t>
   </si>
   <si>
-    <t>起始时间</t>
-  </si>
-  <si>
     <t>飞机票</t>
   </si>
   <si>
@@ -324,6 +321,14 @@
   </si>
   <si>
     <t>empty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>起</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>迄</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -768,10 +773,10 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -820,7 +825,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
         <v>4</v>
@@ -831,7 +836,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s">
         <v>4</v>
@@ -842,10 +847,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C18" t="s">
         <v>35</v>
@@ -853,18 +858,18 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" t="s">
         <v>50</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>51</v>
-      </c>
-      <c r="C19" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -875,211 +880,211 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
         <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>37</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B22" t="s">
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B23" t="s">
         <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B24" t="s">
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B25" t="s">
         <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B26" t="s">
         <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" t="s">
         <v>44</v>
-      </c>
-      <c r="C29" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C30" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" t="s">
         <v>64</v>
-      </c>
-      <c r="B32" t="s">
-        <v>51</v>
-      </c>
-      <c r="C32" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>68</v>
+      </c>
+      <c r="B33" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" t="s">
         <v>69</v>
-      </c>
-      <c r="B33" t="s">
-        <v>51</v>
-      </c>
-      <c r="C33" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C34" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B36" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C36" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B37" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B38" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C38" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B39" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
